--- a/src/data/output/cargo_output.xlsx
+++ b/src/data/output/cargo_output.xlsx
@@ -617,6 +617,31 @@
           <t>TS-007</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0098152</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3933.00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>396.80</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>196.65</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>4526.45</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
